--- a/04_DESIGN_TABLES/DesignTable_6402_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6402_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA16"/>
+  <dimension ref="A1:BA17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="C2" t="n">
         <v>0.50807</v>
@@ -787,25 +787,25 @@
         <v>0.375</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AK2" t="n">
         <v>0.39</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.5715</v>
+        <v>0.6015</v>
       </c>
       <c r="AM2" t="n">
         <v>0.39</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.5985</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5715</v>
+        <v>0.6015</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.705</v>
+        <v>0.765</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.88</v>
@@ -845,7 +845,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1730 = 1.650 (table had 1.59) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1730 = 1.230 (table had 1.17) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.59 -&gt; OMi 1.650 (Items!L1730, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.17 -&gt; OMi 1.230 (Items!P1730, M021)</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -861,7 +866,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="C3" t="n">
         <v>0.32332</v>
@@ -963,25 +968,25 @@
         <v>0.21875</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK3" t="n">
         <v>0.17</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.4725</v>
+        <v>0.4825</v>
       </c>
       <c r="AM3" t="n">
         <v>0.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.4775</v>
+        <v>0.4875</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.4725</v>
+        <v>0.4825</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.605</v>
+        <v>0.625</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.5600000000000001</v>
@@ -1021,7 +1026,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1724 = 1.310 (table had 1.29) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1724 = 0.970 (table had 0.95) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.29 -&gt; OMi 1.310 (Items!L1724, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 0.95 -&gt; OMi 0.970 (Items!P1724, M021)</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1037,7 +1047,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="C4" t="n">
         <v>0.32332</v>
@@ -1139,25 +1149,25 @@
         <v>0.28125</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AK4" t="n">
         <v>0.17</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.4925</v>
+        <v>0.4825</v>
       </c>
       <c r="AM4" t="n">
         <v>0.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.5675</v>
+        <v>0.5575</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.4925</v>
+        <v>0.4825</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.645</v>
+        <v>0.625</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.6899999999999999</v>
@@ -1197,7 +1207,12 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1725 = 1.410 (table had 1.43) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1725 = 1.040 (table had 1.06) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.43 -&gt; OMi 1.410 (Items!L1725, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.06 -&gt; OMi 1.040 (Items!P1725, M021)</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1213,7 +1228,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="C5" t="n">
         <v>0.39837</v>
@@ -1315,25 +1330,25 @@
         <v>0.21875</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AK5" t="n">
         <v>0.172</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.525</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AM5" t="n">
         <v>0.17</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.475</v>
+        <v>0.51</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.525</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.655</v>
+        <v>0.725</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.5600000000000001</v>
@@ -1373,7 +1388,12 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1726 Side 1 ID = 0.172 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1726 Side 1 ID = 0.172 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1726 = 1.410 (table had 1.34) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1726 = 1.070 (table had 1) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.34 -&gt; OMi 1.410 (Items!L1726, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1 -&gt; OMi 1.070 (Items!P1726, M021)</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1389,7 +1409,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="C6" t="n">
         <v>0.39837</v>
@@ -1470,7 +1490,7 @@
         <v>0.246</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AD6" t="n">
         <v>0.215</v>
@@ -1491,25 +1511,25 @@
         <v>0.28125</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AK6" t="n">
         <v>0.3</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.545</v>
+        <v>0.52</v>
       </c>
       <c r="AM6" t="n">
         <v>0.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.545</v>
+        <v>0.52</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.695</v>
+        <v>0.645</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.6899999999999999</v>
@@ -1549,7 +1569,12 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1727 = 1.430 (table had 1.48) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1727 = 1.050 (table had 1.11) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.48 -&gt; OMi 1.430 (Items!L1727, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.11 -&gt; OMi 1.050 (Items!P1727, M021)</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1565,7 +1590,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="C7" t="n">
         <v>0.43301</v>
@@ -1667,25 +1692,25 @@
         <v>0.375</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AK7" t="n">
         <v>0.3</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.495</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AM7" t="n">
         <v>0.39</v>
       </c>
       <c r="AN7" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="AO7" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="AO7" t="n">
-        <v>0.495</v>
-      </c>
       <c r="AP7" t="n">
-        <v>0.595</v>
+        <v>0.735</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.88</v>
@@ -1725,7 +1750,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1728 = 1.620 (table had 1.48) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1728 = 1.200 (table had 1.06) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.48 -&gt; OMi 1.620 (Items!L1728, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.06 -&gt; OMi 1.200 (Items!P1728, M021)</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -1741,7 +1771,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="C8" t="n">
         <v>0.50807</v>
@@ -1843,25 +1873,25 @@
         <v>0.28125</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AK8" t="n">
         <v>0.39</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.6015</v>
+        <v>0.6165</v>
       </c>
       <c r="AM8" t="n">
         <v>0.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.5785</v>
+        <v>0.5935</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.6015</v>
+        <v>0.6165</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.765</v>
+        <v>0.795</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.6899999999999999</v>
@@ -1901,7 +1931,12 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1729 = 1.580 (table had 1.55) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1729 = 1.210 (table had 1.18) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.55 -&gt; OMi 1.580 (Items!L1729, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.18 -&gt; OMi 1.210 (Items!P1729, M021)</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -1917,7 +1952,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="C9" t="n">
         <v>0.50518</v>
@@ -2019,25 +2054,25 @@
         <v>0.4375</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AK9" t="n">
         <v>0.39</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.6315</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="AM9" t="n">
         <v>0.391</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.6785</v>
+        <v>0.6735</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.6315</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.825</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AQ9" t="n">
         <v>1</v>
@@ -2077,7 +2112,12 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); C4HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1731 Hex Flat = 0.875 (table had 0.94); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1731 Side 2 ID = 0.391 (table had 0.48) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); C4HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1731 Hex Flat = 0.875 (table had 0.94); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1731 Side 2 ID = 0.391 (table had 0.48) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1731 = 1.800 (table had 1.81) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1731 = 1.300 (table had 1.31) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.81 -&gt; OMi 1.800 (Items!L1731, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.31 -&gt; OMi 1.300 (Items!P1731, M021)</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2093,7 +2133,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="C10" t="n">
         <v>0.57735</v>
@@ -2195,25 +2235,25 @@
         <v>0.375</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AK10" t="n">
         <v>0.48</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.6665</v>
+        <v>0.7015</v>
       </c>
       <c r="AM10" t="n">
         <v>0.39</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.6335</v>
+        <v>0.6685</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.6665</v>
+        <v>0.7015</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.835</v>
+        <v>0.905</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.88</v>
@@ -2253,7 +2293,12 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1732 = 1.790 (table had 1.72) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1732 = 1.370 (table had 1.3) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.72 -&gt; OMi 1.790 (Items!L1732, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.3 -&gt; OMi 1.370 (Items!P1732, M021)</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -2269,7 +2314,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="C11" t="n">
         <v>0.57735</v>
@@ -2371,25 +2416,25 @@
         <v>0.4375</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AK11" t="n">
         <v>0.48</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.7315</v>
+        <v>0.7015</v>
       </c>
       <c r="AM11" t="n">
         <v>0.48</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.7185</v>
+        <v>0.6885</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.7315</v>
+        <v>0.7015</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.965</v>
+        <v>0.905</v>
       </c>
       <c r="AQ11" t="n">
         <v>1</v>
@@ -2429,7 +2474,12 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1733 = 1.890 (table had 1.95) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1733 = 1.390 (table had 1.45) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.95 -&gt; OMi 1.890 (Items!L1733, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.45 -&gt; OMi 1.390 (Items!P1733, M021)</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -2441,11 +2491,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6402-12-12-O</t>
+          <t>6402-12-10-O</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="C12" t="n">
         <v>0.7216900000000001</v>
@@ -2484,103 +2534,103 @@
         <v>0.08333</v>
       </c>
       <c r="O12" t="n">
-        <v>1.089</v>
+        <v>0.985</v>
       </c>
       <c r="P12" t="n">
-        <v>0.417</v>
+        <v>0.347</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.047</v>
+        <v>0.944</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5928</v>
+        <v>0.4758</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6237</v>
+        <v>0.4988</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5998</v>
+        <v>0.5265</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.57735</v>
       </c>
       <c r="W12" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="X12" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4472</v>
+        <v>0.404</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.549</v>
+        <v>0.4475</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.8623</v>
+        <v>0.7794</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.481</v>
+        <v>0.394</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.4225</v>
+        <v>0.3375</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.97228</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.4851</v>
+        <v>0.4364</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.61</v>
+        <v>0.484</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.8375</v>
+        <v>0.7645</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.61</v>
+        <v>0.484</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.7725</v>
+        <v>0.6555</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.8375</v>
+        <v>0.7645</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.081</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.5998</v>
+        <v>0.5265</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>6402-12-12-O</t>
+          <t>6402-12-10-O</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>Male ORB x Female JIC Swivel Adapter, 1 1/16-12 (male ORB) x 1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>Male ORB x Female JIC Swivel Adapter, 1 1/16-12 (male ORB) x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -2595,7 +2645,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -2605,44 +2655,49 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; L26 / L27 / body hex / nut hex / bores: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.15 on every cell, one source); ORB end from the ORB library; JIC swivel from SWIV_MEAS | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from OMi Items (= the Brennan TFA catalog p.15, one source)</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6402-12-12-O</t>
+          <t>6402-12-10-O</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6402-16-16-O</t>
+          <t>6402-12-12-O</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="C13" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="E13" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="F13" t="n">
         <v>0.469</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5975</v>
+        <v>0.4725</v>
       </c>
       <c r="H13" t="n">
         <v>0.125</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="J13" t="n">
         <v>0.08333</v>
@@ -2660,103 +2715,103 @@
         <v>0.08333</v>
       </c>
       <c r="O13" t="n">
-        <v>1.175</v>
+        <v>1.089</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5485</v>
+        <v>0.417</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.139</v>
+        <v>1.047</v>
       </c>
       <c r="R13" t="n">
-        <v>0.727</v>
+        <v>0.5928</v>
       </c>
       <c r="S13" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0.749</v>
+        <v>0.6237</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="V13" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="X13" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4873</v>
+        <v>0.4472</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.665</v>
+        <v>0.549</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.9544</v>
+        <v>0.8623</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.604</v>
+        <v>0.481</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.5475</v>
+        <v>0.4225</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.5252</v>
+        <v>0.4851</v>
       </c>
       <c r="AG13" t="n">
         <v>0.08333</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.8495</v>
+        <v>0.8225</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.8405</v>
+        <v>0.7575</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.8495</v>
+        <v>0.8225</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.105</v>
+        <v>1.051</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>6402-16-16-O</t>
+          <t>6402-12-12-O</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>Male ORB x Female JIC Swivel Adapter, 1 5/16-12 (male ORB) x 1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>Male ORB x Female JIC Swivel Adapter, 1 1/16-12 (male ORB) x 1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -2766,12 +2821,12 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1 5/16-12 (male ORB)</t>
+          <t>1 1/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2781,44 +2836,49 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1736 = 2.140 (table had 2.17) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1736 = 1.580 (table had 1.61) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.17 -&gt; OMi 2.140 (Items!L1736, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.61 -&gt; OMi 1.580 (Items!P1736, M021)</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6402-16-16-O</t>
+          <t>6402-12-12-O</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6402-20-20-O</t>
+          <t>6402-16-16-O</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="C14" t="n">
-        <v>1.08542</v>
+        <v>0.86603</v>
       </c>
       <c r="D14" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F14" t="n">
         <v>0.469</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="H14" t="n">
         <v>0.125</v>
       </c>
       <c r="I14" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="J14" t="n">
         <v>0.08333</v>
@@ -2836,103 +2896,103 @@
         <v>0.08333</v>
       </c>
       <c r="O14" t="n">
-        <v>1.26</v>
+        <v>1.175</v>
       </c>
       <c r="P14" t="n">
-        <v>0.68</v>
+        <v>0.5485</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.145</v>
+        <v>1.139</v>
       </c>
       <c r="R14" t="n">
-        <v>0.949</v>
+        <v>0.727</v>
       </c>
       <c r="S14" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9889</v>
+        <v>0.749</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5375</v>
+        <v>0.6564</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1547</v>
+        <v>0.86603</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="X14" t="n">
-        <v>0.76739</v>
+        <v>0.61114</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4345</v>
+        <v>0.4873</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.88</v>
+        <v>0.665</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.9556</v>
+        <v>0.9544</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.766</v>
+        <v>0.604</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.7025</v>
+        <v>0.5475</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.53478</v>
+        <v>1.22228</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.4724</v>
+        <v>0.5252</v>
       </c>
       <c r="AG14" t="n">
         <v>0.08333</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.76739</v>
+        <v>0.61114</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.892</v>
+        <v>0.8395</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.8305</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.892</v>
+        <v>0.8395</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.19</v>
+        <v>1.085</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.5375</v>
+        <v>0.6564</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>6402-20-20-O</t>
+          <t>6402-16-16-O</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>Male ORB x Female JIC Swivel Adapter, 1 5/8-12 (male ORB) x 1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>Male ORB x Female JIC Swivel Adapter, 1 5/16-12 (male ORB) x 1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -2942,12 +3002,12 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1 5/8-12 (male ORB)</t>
+          <t>1 5/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2957,44 +3017,49 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1738 = 2.260 (table had 2.28) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1738 = 1.670 (table had 1.69) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.28 -&gt; OMi 2.260 (Items!L1738, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.69 -&gt; OMi 1.670 (Items!P1738, M021)</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6402-20-20-O</t>
+          <t>6402-16-16-O</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6402-24-24-O</t>
+          <t>6402-20-20-O</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="C15" t="n">
-        <v>1.22976</v>
+        <v>1.08542</v>
       </c>
       <c r="D15" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F15" t="n">
         <v>0.469</v>
       </c>
       <c r="G15" t="n">
-        <v>0.878</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="H15" t="n">
         <v>0.125</v>
       </c>
       <c r="I15" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="J15" t="n">
         <v>0.08333</v>
@@ -3012,103 +3077,103 @@
         <v>0.08333</v>
       </c>
       <c r="O15" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>0.776</v>
+        <v>0.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.32</v>
+        <v>1.145</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0504</v>
+        <v>0.949</v>
       </c>
       <c r="S15" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1134</v>
+        <v>0.9889</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7063</v>
+        <v>0.5375</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29904</v>
+        <v>1.1547</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="X15" t="n">
-        <v>0.89239</v>
+        <v>0.76739</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5295</v>
+        <v>0.4345</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.01</v>
+        <v>0.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.065</v>
+        <v>0.9556</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8885</v>
+        <v>0.766</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7025</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.78478</v>
+        <v>1.53478</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.5674</v>
+        <v>0.4724</v>
       </c>
       <c r="AG15" t="n">
         <v>0.08333</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.89239</v>
+        <v>0.76739</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.952</v>
+        <v>0.877</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.038</v>
+        <v>0.923</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.952</v>
+        <v>0.877</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.7063</v>
+        <v>0.5375</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>6402-24-24-O</t>
+          <t>6402-20-20-O</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>Male ORB x Female JIC Swivel Adapter, 1 7/8-12 (male ORB) x 1 7/8-12 (female 37deg JIC swivel)</t>
+          <t>Male ORB x Female JIC Swivel Adapter, 1 5/8-12 (male ORB) x 1 5/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -3118,12 +3183,12 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1 7/8-12 (male ORB)</t>
+          <t>1 5/8-12 (male ORB)</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female 37deg JIC swivel)</t>
+          <t>1 5/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -3133,44 +3198,49 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1739 = 2.420 (table had 2.45) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1739 = 1.800 (table had 1.83) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.45 -&gt; OMi 2.420 (Items!L1739, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.83 -&gt; OMi 1.800 (Items!P1739, M021) | Air-Way nut-face-to-seat 0.620 vs Brennan 0.640</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6402-24-24-O</t>
+          <t>6402-20-20-O</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6402-32-32-O</t>
+          <t>6402-24-24-O</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.93</v>
+        <v>2.61</v>
       </c>
       <c r="C16" t="n">
-        <v>1.58771</v>
+        <v>1.22976</v>
       </c>
       <c r="D16" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="E16" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="F16" t="n">
         <v>0.469</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1905</v>
+        <v>0.878</v>
       </c>
       <c r="H16" t="n">
         <v>0.125</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="J16" t="n">
         <v>0.08333</v>
@@ -3188,131 +3258,317 @@
         <v>0.08333</v>
       </c>
       <c r="O16" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0785</v>
+        <v>0.776</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3936</v>
+        <v>1.0504</v>
       </c>
       <c r="S16" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4242</v>
+        <v>1.1134</v>
       </c>
       <c r="U16" t="n">
-        <v>0.862</v>
+        <v>0.7063</v>
       </c>
       <c r="V16" t="n">
-        <v>1.66277</v>
+        <v>1.29904</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="X16" t="n">
-        <v>1.20489</v>
+        <v>0.89239</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.702</v>
+        <v>0.5295</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.325</v>
+        <v>1.01</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.4202</v>
+        <v>1.065</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.198</v>
+        <v>0.8885</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.1175</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.40978</v>
+        <v>1.78478</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.7399</v>
+        <v>0.5674</v>
       </c>
       <c r="AG16" t="n">
         <v>0.08333</v>
       </c>
       <c r="AH16" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>6402-24-24-O</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>Male ORB x Female JIC Swivel Adapter, 1 7/8-12 (male ORB) x 1 7/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>6402</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1740 = 2.610 (table had 2.72) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1740 = 1.870 (table had 1.99) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.72 -&gt; OMi 2.610 (Items!L1740, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.99 -&gt; OMi 1.870 (Items!P1740, M021)</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>6402-24-24-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6402-32-32-O</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.58771</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.0785</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3936</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.4242</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.20489</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="Y17" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.4202</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.1175</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.40978</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.7399</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.25</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AK16" t="n">
+      <c r="AJ17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.78</v>
       </c>
-      <c r="AL16" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="AM16" t="n">
+      <c r="AL17" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.78</v>
       </c>
-      <c r="AN16" t="n">
-        <v>1.063</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ16" t="n">
+      <c r="AN17" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>2.88</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AR17" t="n">
         <v>0.862</v>
       </c>
-      <c r="AS16" t="inlineStr">
+      <c r="AS17" t="inlineStr">
         <is>
           <t>6402-32-32-O</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr">
+      <c r="AT17" t="inlineStr">
         <is>
           <t>Male ORB x Female JIC Swivel Adapter, 2 1/2-12 (male ORB) x 2 1/2-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="AU16" t="inlineStr">
+      <c r="AU17" t="inlineStr">
         <is>
           <t>6402</t>
         </is>
       </c>
-      <c r="AV16" t="inlineStr">
+      <c r="AV17" t="inlineStr">
         <is>
           <t>2 1/2-12 (male ORB)</t>
         </is>
       </c>
-      <c r="AW16" t="inlineStr">
+      <c r="AW17" t="inlineStr">
         <is>
           <t>2 1/2-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag) | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1741 = 2.950 (table had 2.93) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1741 = 2.010 (table had 1.99) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.93 -&gt; OMi 2.950 (Items!L1741, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.99 -&gt; OMi 2.010 (Items!P1741, M021)</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
         <is>
           <t>6402-32-32-O</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_6402_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6402_SW2.xlsx
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="C2" t="n">
         <v>0.50807</v>
@@ -787,25 +787,25 @@
         <v>0.375</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AK2" t="n">
         <v>0.39</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.6015</v>
+        <v>0.5715</v>
       </c>
       <c r="AM2" t="n">
         <v>0.39</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.5985</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6015</v>
+        <v>0.5715</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.765</v>
+        <v>0.705</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.88</v>
@@ -845,12 +845,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1730 = 1.650 (table had 1.59) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1730 = 1.230 (table had 1.17) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1730 = 1.650 (table had 1.59) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1730 = 1.230 (table had 1.17) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.59 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.65) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.17 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.23) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.59 -&gt; OMi 1.650 (Items!L1730, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.17 -&gt; OMi 1.230 (Items!P1730, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.59 -&gt; OMi 1.650 (Items!L1730, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.17 -&gt; OMi 1.230 (Items!P1730, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.65 -&gt; Air-Way 1.59 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.23 -&gt; Air-Way 1.17</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="C3" t="n">
         <v>0.32332</v>
@@ -968,25 +968,25 @@
         <v>0.21875</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
         <v>0.17</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.4825</v>
+        <v>0.4725</v>
       </c>
       <c r="AM3" t="n">
         <v>0.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.4875</v>
+        <v>0.4775</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.4825</v>
+        <v>0.4725</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.625</v>
+        <v>0.605</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.5600000000000001</v>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1724 = 1.310 (table had 1.29) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1724 = 0.970 (table had 0.95) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1724 = 1.310 (table had 1.29) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1724 = 0.970 (table had 0.95) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.29 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.31) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 0.95 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.97) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.29 -&gt; OMi 1.310 (Items!L1724, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 0.95 -&gt; OMi 0.970 (Items!P1724, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.29 -&gt; OMi 1.310 (Items!L1724, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 0.95 -&gt; OMi 0.970 (Items!P1724, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.31 -&gt; Air-Way 1.29 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 0.97 -&gt; Air-Way 0.95</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="C4" t="n">
         <v>0.32332</v>
@@ -1149,25 +1149,25 @@
         <v>0.28125</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AK4" t="n">
         <v>0.17</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.4825</v>
+        <v>0.4925</v>
       </c>
       <c r="AM4" t="n">
         <v>0.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.5575</v>
+        <v>0.5675</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.4825</v>
+        <v>0.4925</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.625</v>
+        <v>0.645</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.6899999999999999</v>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1725 = 1.410 (table had 1.43) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1725 = 1.040 (table had 1.06) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1725 = 1.410 (table had 1.43) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1725 = 1.040 (table had 1.06) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.43 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.41) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.04) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.43 -&gt; OMi 1.410 (Items!L1725, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.06 -&gt; OMi 1.040 (Items!P1725, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.43 -&gt; OMi 1.410 (Items!L1725, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.06 -&gt; OMi 1.040 (Items!P1725, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.41 -&gt; Air-Way 1.43 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.04 -&gt; Air-Way 1.06</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="C5" t="n">
         <v>0.39837</v>
@@ -1330,25 +1330,25 @@
         <v>0.21875</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.172</v>
+        <v>0.3</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="AM5" t="n">
         <v>0.17</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.51</v>
+        <v>0.475</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.725</v>
+        <v>0.655</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.5600000000000001</v>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1726 Side 1 ID = 0.172 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1726 = 1.410 (table had 1.34) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1726 = 1.070 (table had 1) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1726 Side 1 ID = 0.172 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1726 = 1.410 (table had 1.34) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1726 = 1.070 (table had 1) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.41) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.07) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.172) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.34 -&gt; OMi 1.410 (Items!L1726, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1 -&gt; OMi 1.070 (Items!P1726, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.34 -&gt; OMi 1.410 (Items!L1726, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1 -&gt; OMi 1.070 (Items!P1726, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.41 -&gt; Air-Way 1.34 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.07 -&gt; Air-Way 1 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.172 -&gt; Air-Way 0.3</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="C6" t="n">
         <v>0.39837</v>
@@ -1490,7 +1490,7 @@
         <v>0.246</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="AD6" t="n">
         <v>0.215</v>
@@ -1511,25 +1511,25 @@
         <v>0.28125</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AK6" t="n">
         <v>0.3</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.52</v>
+        <v>0.545</v>
       </c>
       <c r="AM6" t="n">
         <v>0.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.53</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.52</v>
+        <v>0.545</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.645</v>
+        <v>0.695</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.6899999999999999</v>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1727 = 1.430 (table had 1.48) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1727 = 1.050 (table had 1.11) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1727 = 1.430 (table had 1.48) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1727 = 1.050 (table had 1.11) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.48 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.43) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.05) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.48 -&gt; OMi 1.430 (Items!L1727, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.11 -&gt; OMi 1.050 (Items!P1727, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.48 -&gt; OMi 1.430 (Items!L1727, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.11 -&gt; OMi 1.050 (Items!P1727, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.43 -&gt; Air-Way 1.48 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.05 -&gt; Air-Way 1.11</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="C7" t="n">
         <v>0.43301</v>
@@ -1692,25 +1692,25 @@
         <v>0.375</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AK7" t="n">
         <v>0.3</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.495</v>
       </c>
       <c r="AM7" t="n">
         <v>0.39</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.635</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.495</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.735</v>
+        <v>0.595</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.88</v>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1728 = 1.620 (table had 1.48) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1728 = 1.200 (table had 1.06) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1728 = 1.620 (table had 1.48) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1728 = 1.200 (table had 1.06) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.48 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.62) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.48 -&gt; OMi 1.620 (Items!L1728, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.06 -&gt; OMi 1.200 (Items!P1728, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.48 -&gt; OMi 1.620 (Items!L1728, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.06 -&gt; OMi 1.200 (Items!P1728, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.62 -&gt; Air-Way 1.48 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.2 -&gt; Air-Way 1.06</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="C8" t="n">
         <v>0.50807</v>
@@ -1873,25 +1873,25 @@
         <v>0.28125</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AK8" t="n">
         <v>0.39</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.6165</v>
+        <v>0.6015</v>
       </c>
       <c r="AM8" t="n">
         <v>0.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.5935</v>
+        <v>0.5785</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.6165</v>
+        <v>0.6015</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.795</v>
+        <v>0.765</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.6899999999999999</v>
@@ -1931,12 +1931,12 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1729 = 1.580 (table had 1.55) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1729 = 1.210 (table had 1.18) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1729 = 1.580 (table had 1.55) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1729 = 1.210 (table had 1.18) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.55 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.58) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.18 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.21) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.55 -&gt; OMi 1.580 (Items!L1729, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.18 -&gt; OMi 1.210 (Items!P1729, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.55 -&gt; OMi 1.580 (Items!L1729, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.18 -&gt; OMi 1.210 (Items!P1729, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.58 -&gt; Air-Way 1.55 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.21 -&gt; Air-Way 1.18</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -1952,13 +1952,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="C9" t="n">
-        <v>0.50518</v>
+        <v>0.54271</v>
       </c>
       <c r="D9" t="n">
-        <v>0.875</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>0.375</v>
@@ -2054,25 +2054,25 @@
         <v>0.4375</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AK9" t="n">
         <v>0.39</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6315</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.391</v>
+        <v>0.48</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.6735</v>
+        <v>0.6785</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6315</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="AQ9" t="n">
         <v>1</v>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); C4HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1731 Hex Flat = 0.875 (table had 0.94); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1731 Side 2 ID = 0.391 (table had 0.48) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1731 = 1.800 (table had 1.81) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1731 = 1.300 (table had 1.31) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); C4HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1731 Hex Flat = 0.875 (table had 0.94); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1731 Side 2 ID = 0.391 (table had 0.48) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1731 = 1.800 (table had 1.81) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1731 = 1.300 (table had 1.31) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.31 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.3) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C4HEX@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D2@BORE: Air-Way 0.48 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.81 -&gt; OMi 1.800 (Items!L1731, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.31 -&gt; OMi 1.300 (Items!P1731, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.81 -&gt; OMi 1.800 (Items!L1731, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.31 -&gt; OMi 1.300 (Items!P1731, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.8 -&gt; Air-Way 1.81 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.3 -&gt; Air-Way 1.31 | 2026-10-20 Air-Way first: C4HEX@HEX OMi/Brennan 0.875 -&gt; Air-Way 0.94 | 2026-10-20 Air-Way first: D2@BORE OMi/Brennan 0.391 -&gt; Air-Way 0.48</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="C10" t="n">
         <v>0.57735</v>
@@ -2235,25 +2235,25 @@
         <v>0.375</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AK10" t="n">
         <v>0.48</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.7015</v>
+        <v>0.6665</v>
       </c>
       <c r="AM10" t="n">
         <v>0.39</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.6685</v>
+        <v>0.6335</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.7015</v>
+        <v>0.6665</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.905</v>
+        <v>0.835</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.88</v>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1732 = 1.790 (table had 1.72) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1732 = 1.370 (table had 1.3) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1732 = 1.790 (table had 1.72) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1732 = 1.370 (table had 1.3) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.79) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.37) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.72 -&gt; OMi 1.790 (Items!L1732, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.3 -&gt; OMi 1.370 (Items!P1732, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.72 -&gt; OMi 1.790 (Items!L1732, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.3 -&gt; OMi 1.370 (Items!P1732, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.79 -&gt; Air-Way 1.72 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.37 -&gt; Air-Way 1.3</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="C11" t="n">
         <v>0.57735</v>
@@ -2416,25 +2416,25 @@
         <v>0.4375</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AK11" t="n">
         <v>0.48</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.7015</v>
+        <v>0.7315</v>
       </c>
       <c r="AM11" t="n">
         <v>0.48</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.6885</v>
+        <v>0.7185</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.7015</v>
+        <v>0.7315</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.905</v>
+        <v>0.965</v>
       </c>
       <c r="AQ11" t="n">
         <v>1</v>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1733 = 1.890 (table had 1.95) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1733 = 1.390 (table had 1.45) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1733 = 1.890 (table had 1.95) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1733 = 1.390 (table had 1.45) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.95 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.89) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.45 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.39) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.95 -&gt; OMi 1.890 (Items!L1733, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.45 -&gt; OMi 1.390 (Items!P1733, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.95 -&gt; OMi 1.890 (Items!L1733, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.45 -&gt; OMi 1.390 (Items!P1733, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.89 -&gt; Air-Way 1.95 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.39 -&gt; Air-Way 1.45</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="C13" t="n">
         <v>0.7216900000000001</v>
@@ -2778,25 +2778,25 @@
         <v>0.53125</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AK13" t="n">
         <v>0.61</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.8225</v>
+        <v>0.8375</v>
       </c>
       <c r="AM13" t="n">
         <v>0.61</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.7575</v>
+        <v>0.7725</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.8225</v>
+        <v>0.8375</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.051</v>
+        <v>1.081</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.25</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1736 = 2.140 (table had 2.17) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1736 = 1.580 (table had 1.61) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1736 = 2.140 (table had 2.17) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1736 = 1.580 (table had 1.61) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 2.17 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.61 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.58) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.17 -&gt; OMi 2.140 (Items!L1736, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.61 -&gt; OMi 1.580 (Items!P1736, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.17 -&gt; OMi 2.140 (Items!L1736, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.61 -&gt; OMi 1.580 (Items!P1736, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 2.14 -&gt; Air-Way 2.17 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.58 -&gt; Air-Way 1.61</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="C14" t="n">
         <v>0.86603</v>
@@ -2959,25 +2959,25 @@
         <v>0.65625</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AK14" t="n">
         <v>0.84</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.8395</v>
+        <v>0.8495</v>
       </c>
       <c r="AM14" t="n">
         <v>0.84</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.8305</v>
+        <v>0.8405</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.8395</v>
+        <v>0.8495</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.085</v>
+        <v>1.105</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.5</v>
@@ -3017,12 +3017,12 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1738 = 2.260 (table had 2.28) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1738 = 1.670 (table had 1.69) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1738 = 2.260 (table had 2.28) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1738 = 1.670 (table had 1.69) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 2.28 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.26) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.69 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.67) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.28 -&gt; OMi 2.260 (Items!L1738, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.69 -&gt; OMi 1.670 (Items!P1738, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.28 -&gt; OMi 2.260 (Items!L1738, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.69 -&gt; OMi 1.670 (Items!P1738, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 2.26 -&gt; Air-Way 2.28 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.67 -&gt; Air-Way 1.69</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="C15" t="n">
         <v>1.08542</v>
@@ -3140,25 +3140,25 @@
         <v>0.8125</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AK15" t="n">
         <v>1.08</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.877</v>
+        <v>0.892</v>
       </c>
       <c r="AM15" t="n">
         <v>1.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.923</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.877</v>
+        <v>0.892</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AQ15" t="n">
         <v>2</v>
@@ -3198,12 +3198,12 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1739 = 2.420 (table had 2.45) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1739 = 1.800 (table had 1.83) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1739 = 2.420 (table had 2.45) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1739 = 1.800 (table had 1.83) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 2.45 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.42) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.83 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.45 -&gt; OMi 2.420 (Items!L1739, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.83 -&gt; OMi 1.800 (Items!P1739, M021) | Air-Way nut-face-to-seat 0.620 vs Brennan 0.640</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.45 -&gt; OMi 2.420 (Items!L1739, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.83 -&gt; OMi 1.800 (Items!P1739, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 2.42 -&gt; Air-Way 2.45 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.8 -&gt; Air-Way 1.83</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="C16" t="n">
         <v>1.22976</v>
@@ -3300,7 +3300,7 @@
         <v>0.8885</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="AD16" t="n">
         <v>0.8100000000000001</v>
@@ -3321,25 +3321,25 @@
         <v>0.9375</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="AK16" t="n">
         <v>1.31</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.897</v>
+        <v>0.952</v>
       </c>
       <c r="AM16" t="n">
         <v>1.31</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.973</v>
+        <v>1.038</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.897</v>
+        <v>0.952</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ16" t="n">
         <v>2.25</v>
@@ -3379,12 +3379,12 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1740 = 2.610 (table had 2.72) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1740 = 1.870 (table had 1.99) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1740 = 2.610 (table had 2.72) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1740 = 1.870 (table had 1.99) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 2.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.61) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.99 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.87) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.72 -&gt; OMi 2.610 (Items!L1740, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.99 -&gt; OMi 1.870 (Items!P1740, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.72 -&gt; OMi 2.610 (Items!L1740, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.99 -&gt; OMi 1.870 (Items!P1740, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 2.61 -&gt; Air-Way 2.72 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.87 -&gt; Air-Way 1.99</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="C17" t="n">
         <v>1.58771</v>
@@ -3502,25 +3502,25 @@
         <v>1.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="AK17" t="n">
         <v>1.78</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="AM17" t="n">
         <v>1.78</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.073</v>
+        <v>1.063</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AQ17" t="n">
         <v>2.88</v>
@@ -3560,12 +3560,12 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1741 = 2.950 (table had 2.93) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1741 = 2.010 (table had 1.99) [user 2026-10-18 A19] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1741 = 2.950 (table had 2.93) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1741 = 2.010 (table had 1.99) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 2.93 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.95) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.99 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.01) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male ORB end: thread length + groove from the 6401/6405/6410 review tables (ORD-5700 groove, measured thread length; no tip chamfer modelled); L26 = ORB tip to the nut face, L27 = ORB tip to the seat; body hex C4, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.93 -&gt; OMi 2.950 (Items!L1741, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.99 -&gt; OMi 2.010 (Items!P1741, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.93 -&gt; OMi 2.950 (Items!L1741, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.99 -&gt; OMi 2.010 (Items!P1741, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 2.95 -&gt; Air-Way 2.93 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 2.01 -&gt; Air-Way 1.99</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
